--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260811.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260811.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>138,585</t>
+          <t>138,385</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>29.86%</t>
+          <t>29.44%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>15,785</t>
+          <t>15,685</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.97%</t>
+          <t>8.11%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>100,320</t>
+          <t>100,120</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.72%</t>
+          <t>7.44%</t>
         </is>
       </c>
     </row>
@@ -677,56 +677,56 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>51,065</t>
+          <t>50,865</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.52%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>NEE US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>121,895</t>
+          <t>343,004,636</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>5.43%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>NEE US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>59,930</t>
+          <t>121,695</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>5.33%</t>
         </is>
       </c>
     </row>
@@ -743,144 +743,144 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>7,486,042</t>
+          <t>9,865,883</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>5.04%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>65,935</t>
+          <t>59,930</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.91%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>65,835</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>18,373</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>45,365</t>
+          <t>18,373</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>19,825</t>
+          <t>45,265</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>160,671,600</t>
+          <t>19,825</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>31,760</t>
+          <t>31,660</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -963,78 +963,78 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>51,345</t>
+          <t>51,245</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>26,658</t>
+          <t>19,530</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>36,400</t>
+          <t>26,658</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>19,530</t>
+          <t>36,400</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1122,51 +1122,51 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>127,675</t>
+          <t>11,701</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>11,701</t>
+          <t>127,475</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>483,561,000</t>
+          <t>290,526,720</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>8,679,840</t>
+          <t>316,535</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
